--- a/Credit-Scoring.xlsx
+++ b/Credit-Scoring.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="544">
   <si>
     <t>S.N</t>
   </si>
@@ -1481,16 +1481,37 @@
     <t>Answers JSON</t>
   </si>
   <si>
-    <t>2026-03-16T07:10:26.209Z</t>
+    <t>Submission ID</t>
+  </si>
+  <si>
+    <t>Approver Status</t>
+  </si>
+  <si>
+    <t>Approver Notes</t>
+  </si>
+  <si>
+    <t>Approver Decided At</t>
+  </si>
+  <si>
+    <t>2026-03-18T03:50:18.310Z</t>
   </si>
   <si>
     <t>D Risk</t>
   </si>
   <si>
-    <t>{"type_collection":"collection","type_processing":"processing","cust_new":"new","cust_existing":"existing","coop_name":"Dummy","model_type":"Milk Collection Only (Model A)","loan_type":"New Loan","years_operation":0,"office_location":"","existing_loan":1520000,"proposed_loan":200000,"total_loan":1720000,"interest_rate":0,"loan_tenure":0,"installment_freq":"Monthly","primary_land_value":0,"milk_sales":0,"other_product_sales":0,"other_income":0,"total_sales":0,"grant_income":0,"total_revenue":0,"bank_sales":0,"total_buyers":0,"top5_buyers_sales":0,"largest_buyer_sales":0,"top5_buyer_pct":0,"largest_buyer_pct":0,"avg_collection_days":0,"raw_milk_cost":0,"processing_cost":0,"packaging_cost":0,"transport_cost":0,"other_processing_cost":0,"salary_expense":0,"admin_expense":0,"electricity_expense":0,"fuel_expense":0,"repair_expense":0,"rent_expense":0,"other_opex":0,"total_opex":0,"annual_depreciation":0,"amortization_amount":0,"cash_last_year":0,"cash_prev_year":0,"lowest_monthly_expense":0,"income_expense_checked":"","audit_observations":0,"avg_inventory_value":0,"cash_hand":0,"bank_balance":0,"total_cash":0,"accounts_receivable":0,"inventory_value":0,"prepaid_expenses":0,"other_current_assets":0,"total_current_assets":0,"land_value":0,"building_value":0,"machinery_value":0,"vehicle_value":0,"furniture_value":0,"other_fixed_assets":0,"total_fixed_assets":0,"total_assets":0,"accounts_payable":0,"short_term_loan":0,"accrued_expenses":0,"current_ltd":0,"total_current_liabilities":0,"long_term_loan":0,"other_ltl":0,"total_long_term_liabilities":0,"total_liabilities":0,"paid_up_capital":0,"retained_earnings":0,"reserve_fund":0,"total_net_worth":0,"total_milk_collected":0,"milk_loss":0,"processing_loss":0,"total_milk_sold":0,"avg_monthly_milk":0,"lowest_monthly_milk":0,"collection_days":0,"total_farmers":0,"avg_milk_per_farmer":0,"top5_farmers_milk":0,"vehicle_avail_pct":0,"storage_cold_facility":"","digital_mis_pos":"","quality_sop_score":0,"total_member_loans":0,"npa_member_loans":0,"max_dpd_members":0,"restructured_loans_3yr":"","mgmt_experience":0,"internal_control_score":0,"loan_policy_compliance":"","meeting_frequency":"","insurance_available":"","regulatory_compliance":"","climatic_risk_score":0,"credit_history_bfi":"","max_dpd_bfi":0,"community_support_level":"","emergency_response":"","farmer_training_freq":""}</t>
-  </si>
-  <si>
-    <t>2026-03-16T07:18:24.170Z</t>
+    <t>Failing Test Cooperative (Test)</t>
+  </si>
+  <si>
+    <t>{"model_type":"","loan_type":"","coop_name":"Failing Test Cooperative (Test)","years_operation":1,"office_location":"Remote District","total_loan":"9000000","existing_loan":3000000,"proposed_loan":6000000,"interest_rate":16,"loan_tenure":36,"installment_freq":"Annual","primary_land_value":2000000,"total_sales":"8100000","total_revenue":"13100000","milk_sales":8000000,"other_product_sales":0,"other_income":100000,"grant_income":5000000,"bank_sales":2000000,"top5_buyer_pct":"80.25","largest_buyer_pct":"49.38","total_buyers":50,"top5_buyers_sales":6500000,"largest_buyer_sales":4000000,"gov_buyer_sales":500000,"no_govt_buyers":1,"large_private_buyer_sales":3000000,"no_private_sector_buyer":2,"small_buyer_sales":2000000,"no_small_buyer_sales":20,"avg_collection_days":90,"contract_coverage":0,"total_opex":"9110000","raw_milk_cost":7000000,"processing_cost":0,"packaging_cost":0,"transport_cost":300000,"other_processing_cost":0,"salary_expense":900000,"admin_expense":300000,"electricity_expense":150000,"fuel_expense":120000,"repair_expense":80000,"rent_expense":60000,"other_opex":200000,"lowest_monthly_expense":700000,"annual_depreciation":200000,"amortization_amount":0,"total_cash":"400000","total_current_assets":"3100000","total_fixed_assets":"3230000","total_assets":"6330000","cash_hand":50000,"bank_balance":350000,"accounts_receivable":2500000,"inventory_value":150000,"prepaid_expenses":0,"other_current_assets":50000,"land_value":1800000,"building_value":600000,"machinery_value":400000,"vehicle_value":300000,"furniture_value":80000,"other_fixed_assets":50000,"total_current_liabilities":"6300000","total_long_term_liabilities":"5800000","total_liabilities":"12100000","accounts_payable":1500000,"short_term_loan":3000000,"accrued_expenses":600000,"current_ltd":1200000,"long_term_loan":4800000,"other_ltl":1000000,"total_net_worth":"400000","paid_up_capital":500000,"retained_earnings":-200000,"reserve_fund":100000,"total_milk_sold":"630000","avg_milk_per_farmer":"7777.78","total_milk_collected":700000,"milk_loss":70000,"processing_loss":0,"avg_monthly_milk":58000,"lowest_monthly_milk":20000,"highest_monthly_milk":90000,"avg_inventory_value":100000,"credit_period_given_days":45,"top5_farmers_milk":420000,"highest_farmer_qty":30000,"lowest_farmer_qty":200,"total_farmers":90,"collection_days":260,"total_member_loans":2000000,"npa_member_loans":600000,"overdue_member_loans":800000,"restructured_loans_3yr":"Frequently","max_dpd_members":120,"credit_history_flag":"Frequent delays","cash_last_year":400000,"cash_prev_year":700000,"audit_observations":10,"mgmt_experience":1,"internal_control_score":"20","loan_policy_compliance":"No","vehicle_avail_pct":"No","storage_cold_facility":"No","quality_sop_score":"15","insurance_available":"No","digital_mis_pos":"No","regulatory_compliance":"No","climatic_risk_score":"8","credit_history_bfi":"Substandard","max_dpd_bfi":45,"meeting_frequency":"Rarely","member_info_transparency":"Decided among few","fund_usage":"Other things","kyc_aml":"Hard","income_expense_checked":"Never","right_to_information":"Only after implementation","community_support_level":"Minimal","emergency_response":"No Plan","customer_type":"new"}</t>
+  </si>
+  <si>
+    <t>SUB-DA4645BB-B2D</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>2026-03-18T03:54:07.098Z</t>
   </si>
   <si>
     <t>A Risk</t>
@@ -1499,10 +1520,46 @@
     <t>Himalayan Dairy Cooperative (Test)</t>
   </si>
   <si>
-    <t>{"type_collection":"collection","type_processing":"processing","cust_new":"new","cust_existing":"existing","coop_name":"Himalayan Dairy Cooperative (Test)","model_type":"Milk Collection Only (Model A)","loan_type":"New Loan","years_operation":15,"office_location":"Lalitpur, Bagmati","existing_loan":0,"proposed_loan":3000000,"total_loan":3000000,"interest_rate":9,"loan_tenure":60,"installment_freq":"Monthly","primary_land_value":9000000,"milk_sales":42000000,"other_product_sales":3000000,"other_income":500000,"total_sales":45500000,"grant_income":200000,"total_revenue":45700000,"bank_sales":38000000,"total_buyers":500,"top5_buyers_sales":10000000,"largest_buyer_sales":2500000,"top5_buyer_pct":22,"largest_buyer_pct":5.5,"avg_collection_days":20,"raw_milk_cost":28000000,"processing_cost":0,"packaging_cost":0,"transport_cost":600000,"other_processing_cost":0,"salary_expense":2000000,"admin_expense":500000,"electricity_expense":300000,"fuel_expense":200000,"repair_expense":150000,"rent_expense":100000,"other_opex":200000,"total_opex":32050000,"annual_depreciation":800000,"amortization_amount":100000,"cash_last_year":5500000,"cash_prev_year":4200000,"lowest_monthly_expense":250000,"income_expense_checked":"Regularly","audit_observations":0,"avg_inventory_value":400000,"cash_hand":500000,"bank_balance":5000000,"total_cash":5500000,"accounts_receivable":800000,"inventory_value":600000,"prepaid_expenses":100000,"other_current_assets":200000,"total_current_assets":7200000,"land_value":8000000,"building_value":3000000,"machinery_value":2500000,"vehicle_value":1500000,"furniture_value":300000,"other_fixed_assets":200000,"total_fixed_assets":15500000,"total_assets":22700000,"accounts_payable":300000,"short_term_loan":0,"accrued_expenses":100000,"current_ltd":600000,"total_current_liabilities":1000000,"long_term_loan":2400000,"other_ltl":0,"total_long_term_liabilities":2400000,"total_liabilities":3400000,"paid_up_capital":5000000,"retained_earnings":4000000,"reserve_fund":2000000,"total_net_worth":11000000,"total_milk_collected":4200000,"milk_loss":42000,"processing_loss":0,"total_milk_sold":4158000,"avg_monthly_milk":350000,"lowest_monthly_milk":310000,"collection_days":355,"total_farmers":700,"avg_milk_per_farmer":6000,"top5_farmers_milk":500000,"vehicle_avail_pct":95,"storage_cold_facility":"Yes","digital_mis_pos":"Yes","quality_sop_score":88,"total_member_loans":8000000,"npa_member_loans":80000,"max_dpd_members":10,"restructured_loans_3yr":"None","mgmt_experience":12,"internal_control_score":85,"loan_policy_compliance":"Yes","meeting_frequency":"Weekly","insurance_available":"Yes","regulatory_compliance":"Yes","climatic_risk_score":2,"credit_history_bfi":"Pass","max_dpd_bfi":0,"community_support_level":"Significant","emergency_response":"Proper Plan","farmer_training_freq":""}</t>
-  </si>
-  <si>
-    <t>2026-03-16T07:19:10.627Z</t>
+    <t>{"model_type":"","loan_type":"","coop_name":"Himalayan Dairy Cooperative (Test)","years_operation":15,"office_location":"Lalitpur, Bagmati","total_loan":"3000000","existing_loan":0,"proposed_loan":3000000,"interest_rate":9,"loan_tenure":60,"installment_freq":"Monthly","primary_land_value":9000000,"total_sales":"45500000","total_revenue":"45700000","milk_sales":42000000,"other_product_sales":3000000,"other_income":500000,"grant_income":200000,"bank_sales":38000000,"top5_buyer_pct":"21.98","largest_buyer_pct":"5.49","total_buyers":500,"top5_buyers_sales":10000000,"largest_buyer_sales":2500000,"gov_buyer_sales":8000000,"no_govt_buyers":3,"large_private_buyer_sales":20000000,"no_private_sector_buyer":5,"small_buyer_sales":500000,"no_small_buyer_sales":10,"avg_collection_days":20,"contract_coverage":8,"total_opex":"32050000","raw_milk_cost":28000000,"processing_cost":0,"packaging_cost":0,"transport_cost":600000,"other_processing_cost":0,"salary_expense":2000000,"admin_expense":500000,"electricity_expense":300000,"fuel_expense":200000,"repair_expense":150000,"rent_expense":100000,"other_opex":200000,"lowest_monthly_expense":250000,"annual_depreciation":800000,"amortization_amount":100000,"total_cash":"5500000","total_current_assets":"7200000","total_fixed_assets":"15500000","total_assets":"22700000","cash_hand":500000,"bank_balance":5000000,"accounts_receivable":800000,"inventory_value":600000,"prepaid_expenses":100000,"other_current_assets":200000,"land_value":8000000,"building_value":3000000,"machinery_value":2500000,"vehicle_value":1500000,"furniture_value":300000,"other_fixed_assets":200000,"total_current_liabilities":"1000000","total_long_term_liabilities":"2400000","total_liabilities":"3400000","accounts_payable":300000,"short_term_loan":0,"accrued_expenses":100000,"current_ltd":600000,"long_term_loan":2400000,"other_ltl":0,"total_net_worth":"11000000","paid_up_capital":5000000,"retained_earnings":4000000,"reserve_fund":2000000,"total_milk_sold":"4158000","avg_milk_per_farmer":"6000","total_milk_collected":4200000,"milk_loss":42000,"processing_loss":0,"avg_monthly_milk":350000,"lowest_monthly_milk":310000,"highest_monthly_milk":420000,"avg_inventory_value":400000,"credit_period_given_days":7,"top5_farmers_milk":500000,"highest_farmer_qty":90000,"lowest_farmer_qty":1000,"total_farmers":700,"collection_days":355,"total_member_loans":8000000,"npa_member_loans":80000,"overdue_member_loans":120000,"restructured_loans_3yr":"None","max_dpd_members":10,"credit_history_flag":"Timely","cash_last_year":5500000,"cash_prev_year":4200000,"audit_observations":0,"mgmt_experience":12,"internal_control_score":"85","loan_policy_compliance":"Yes","vehicle_avail_pct":"Yes","storage_cold_facility":"Yes","quality_sop_score":"85","insurance_available":"Yes","digital_mis_pos":"Yes","regulatory_compliance":"Yes","climatic_risk_score":"2","credit_history_bfi":"Pass","max_dpd_bfi":0,"meeting_frequency":"Weekly","member_info_transparency":"Always","fund_usage":"Buying Milk","kyc_aml":"Easily Found","income_expense_checked":"Regularly","right_to_information":"Always Beforehand","community_support_level":"Significant","emergency_response":"Proper Plan","customer_type":"existing"}</t>
+  </si>
+  <si>
+    <t>SUB-D5192A51-F19</t>
+  </si>
+  <si>
+    <t>2026-03-18T04:20:13.799Z</t>
+  </si>
+  <si>
+    <t>{"model_type":"","loan_type":"","coop_name":"Himalayan Dairy Cooperative (Test)","years_operation":15,"office_location":"Lalitpur, Bagmati","total_loan":"3000000","existing_loan":0,"proposed_loan":3000000,"interest_rate":9,"loan_tenure":60,"installment_freq":"Monthly","primary_land_value":9000000,"total_sales":"45500000","total_revenue":"45700000","milk_sales":42000000,"other_product_sales":3000000,"other_income":500000,"grant_income":200000,"bank_sales":38000000,"top5_buyer_pct":"21.98","largest_buyer_pct":"5.49","total_buyers":500,"top5_buyers_sales":10000000,"largest_buyer_sales":2500000,"gov_buyer_sales":8000000,"no_govt_buyers":3,"large_private_buyer_sales":20000000,"no_private_sector_buyer":5,"small_buyer_sales":500000,"no_small_buyer_sales":10,"avg_collection_days":20,"contract_coverage":8,"total_opex":"32050000","raw_milk_cost":28000000,"processing_cost":0,"packaging_cost":0,"transport_cost":600000,"other_processing_cost":0,"salary_expense":2000000,"admin_expense":500000,"electricity_expense":300000,"fuel_expense":200000,"repair_expense":150000,"rent_expense":100000,"other_opex":200000,"lowest_monthly_expense":250000,"annual_depreciation":800000,"amortization_amount":100000,"total_cash":"5500000","total_current_assets":"7200000","total_fixed_assets":"15500000","total_assets":"22700000","cash_hand":500000,"bank_balance":5000000,"accounts_receivable":800000,"inventory_value":600000,"prepaid_expenses":100000,"other_current_assets":200000,"land_value":8000000,"building_value":3000000,"machinery_value":2500000,"vehicle_value":1500000,"furniture_value":300000,"other_fixed_assets":200000,"total_current_liabilities":"1000000","total_long_term_liabilities":"2400000","total_liabilities":"3400000","accounts_payable":300000,"short_term_loan":0,"accrued_expenses":100000,"current_ltd":600000,"long_term_loan":2400000,"other_ltl":0,"total_net_worth":"11000000","paid_up_capital":5000000,"retained_earnings":4000000,"reserve_fund":2000000,"total_milk_sold":"4158000","avg_milk_per_farmer":"6000","total_milk_collected":4200000,"milk_loss":42000,"processing_loss":0,"avg_monthly_milk":350000,"lowest_monthly_milk":310000,"highest_monthly_milk":420000,"avg_inventory_value":400000,"credit_period_given_days":7,"top5_farmers_milk":500000,"highest_farmer_qty":90000,"lowest_farmer_qty":1000,"total_farmers":700,"collection_days":355,"total_member_loans":8000000,"npa_member_loans":80000,"overdue_member_loans":120000,"restructured_loans_3yr":"None","max_dpd_members":10,"credit_history_flag":"Timely","cash_last_year":5500000,"cash_prev_year":4200000,"audit_observations":0,"mgmt_experience":12,"internal_control_score":"85","loan_policy_compliance":"Yes","vehicle_avail_pct":"Yes","storage_cold_facility":"Yes","quality_sop_score":"85","insurance_available":"Yes","digital_mis_pos":"Yes","regulatory_compliance":"Yes","climatic_risk_score":"2","credit_history_bfi":"Pass","max_dpd_bfi":0,"meeting_frequency":"Weekly","member_info_transparency":"Always","fund_usage":"Buying Milk","kyc_aml":"Easily Found","income_expense_checked":"Regularly","right_to_information":"Always Beforehand","community_support_level":"Significant","emergency_response":"Proper Plan","customer_type":"new"}</t>
+  </si>
+  <si>
+    <t>SUB-5C8A7791-7B4</t>
+  </si>
+  <si>
+    <t>2026-03-18T04:35:25.015Z</t>
+  </si>
+  <si>
+    <t>C Risk</t>
+  </si>
+  <si>
+    <t>Koshi Valley Cooperative (Test)</t>
+  </si>
+  <si>
+    <t>{"model_type":"","loan_type":"","coop_name":"Koshi Valley Cooperative (Test)","years_operation":4,"office_location":"Morang, Koshi","total_loan":"6500000","existing_loan":1500000,"proposed_loan":5000000,"interest_rate":12,"loan_tenure":48,"installment_freq":"Quarterly","primary_land_value":5000000,"total_sales":"18700000","total_revenue":"21200000","milk_sales":18000000,"other_product_sales":500000,"other_income":200000,"grant_income":2500000,"bank_sales":9000000,"top5_buyer_pct":"53.48","largest_buyer_pct":"26.74","total_buyers":150,"top5_buyers_sales":10000000,"largest_buyer_sales":5000000,"gov_buyer_sales":2000000,"no_govt_buyers":1,"large_private_buyer_sales":8000000,"no_private_sector_buyer":3,"small_buyer_sales":1000000,"no_small_buyer_sales":15,"avg_collection_days":55,"contract_coverage":2,"total_opex":"15730000","raw_milk_cost":13000000,"processing_cost":0,"packaging_cost":0,"transport_cost":400000,"other_processing_cost":0,"salary_expense":1200000,"admin_expense":350000,"electricity_expense":200000,"fuel_expense":150000,"repair_expense":100000,"rent_expense":80000,"other_opex":250000,"lowest_monthly_expense":400000,"annual_depreciation":400000,"amortization_amount":30000,"total_cash":"1500000","total_current_assets":"3450000","total_fixed_assets":"6850000","total_assets":"10300000","cash_hand":200000,"bank_balance":1300000,"accounts_receivable":1500000,"inventory_value":300000,"prepaid_expenses":50000,"other_current_assets":100000,"land_value":4000000,"building_value":1200000,"machinery_value":800000,"vehicle_value":600000,"furniture_value":150000,"other_fixed_assets":100000,"total_current_liabilities":"3600000","total_long_term_liabilities":"4500000","total_liabilities":"8100000","accounts_payable":800000,"short_term_loan":1500000,"accrued_expenses":300000,"current_ltd":1000000,"long_term_loan":4000000,"other_ltl":500000,"total_net_worth":"2300000","paid_up_capital":1500000,"retained_earnings":500000,"reserve_fund":300000,"total_milk_sold":"1520000","avg_milk_per_farmer":"5714.29","total_milk_collected":1600000,"milk_loss":80000,"processing_loss":0,"avg_monthly_milk":133000,"lowest_monthly_milk":80000,"highest_monthly_milk":180000,"avg_inventory_value":200000,"credit_period_given_days":21,"top5_farmers_milk":640000,"highest_farmer_qty":50000,"lowest_farmer_qty":500,"total_farmers":280,"collection_days":310,"total_member_loans":3500000,"npa_member_loans":280000,"overdue_member_loans":400000,"restructured_loans_3yr":"Few Times","max_dpd_members":65,"credit_history_flag":"With few delays","cash_last_year":1500000,"cash_prev_year":1800000,"audit_observations":5,"mgmt_experience":4,"internal_control_score":"20","loan_policy_compliance":"No","vehicle_avail_pct":"Yes","storage_cold_facility":"No","quality_sop_score":"65","insurance_available":"No","digital_mis_pos":"Partial","regulatory_compliance":"Partial","climatic_risk_score":"5","credit_history_bfi":"Watch List","max_dpd_bfi":10,"meeting_frequency":"Monthly","member_info_transparency":"Sometimes","fund_usage":"Buying Milk","kyc_aml":"Sometimes","income_expense_checked":"Occasionally","right_to_information":"Sometimes beforehand","community_support_level":"Moderate","emergency_response":"Ad-hoc","customer_type":"new"}</t>
+  </si>
+  <si>
+    <t>SUB-5B5DFB97-694</t>
+  </si>
+  <si>
+    <t>rejected</t>
+  </si>
+  <si>
+    <t>tesT</t>
+  </si>
+  <si>
+    <t>2026-03-18T05:05:35.778Z</t>
+  </si>
+  <si>
+    <t>2026-03-18T04:37:19.814Z</t>
   </si>
   <si>
     <t>B Risk</t>
@@ -1511,55 +1568,49 @@
     <t>Terai Milk Cooperative (Test)</t>
   </si>
   <si>
-    <t>{"type_collection":"collection","type_processing":"processing","cust_new":"new","cust_existing":"existing","coop_name":"Terai Milk Cooperative (Test)","model_type":"Milk Collection Only (Model A)","loan_type":"New Loan","years_operation":8,"office_location":"Chitwan, Bagmati","existing_loan":500000,"proposed_loan":4000000,"total_loan":4500000,"interest_rate":10,"loan_tenure":60,"installment_freq":"Monthly","primary_land_value":7000000,"milk_sales":30000000,"other_product_sales":1500000,"other_income":300000,"total_sales":31800000,"grant_income":800000,"total_revenue":32600000,"bank_sales":22000000,"total_buyers":300,"top5_buyers_sales":12000000,"largest_buyer_sales":4000000,"top5_buyer_pct":37.7,"largest_buyer_pct":12.6,"avg_collection_days":35,"raw_milk_cost":20000000,"processing_cost":0,"packaging_cost":0,"transport_cost":500000,"other_processing_cost":0,"salary_expense":1500000,"admin_expense":400000,"electricity_expense":250000,"fuel_expense":180000,"repair_expense":120000,"rent_expense":100000,"other_opex":300000,"total_opex":23350000,"annual_depreciation":600000,"amortization_amount":50000,"cash_last_year":3200000,"cash_prev_year":2800000,"lowest_monthly_expense":300000,"income_expense_checked":"Regularly","audit_observations":2,"avg_inventory_value":300000,"cash_hand":300000,"bank_balance":2900000,"total_cash":3200000,"accounts_receivable":1000000,"inventory_value":400000,"prepaid_expenses":80000,"other_current_assets":150000,"total_current_assets":4830000,"land_value":6000000,"building_value":2000000,"machinery_value":1500000,"vehicle_value":1200000,"furniture_value":200000,"other_fixed_assets":150000,"total_fixed_assets":11050000,"total_assets":15880000,"accounts_payable":500000,"short_term_loan":500000,"accrued_expenses":150000,"current_ltd":800000,"total_current_liabilities":1950000,"long_term_loan":3200000,"other_ltl":0,"total_long_term_liabilities":3200000,"total_liabilities":5150000,"paid_up_capital":3000000,"retained_earnings":2000000,"reserve_fund":1000000,"total_net_worth":6000000,"total_milk_collected":2800000,"milk_loss":70000,"processing_loss":0,"total_milk_sold":2730000,"avg_monthly_milk":233000,"lowest_monthly_milk":180000,"collection_days":340,"total_farmers":450,"avg_milk_per_farmer":6222.2,"top5_farmers_milk":560000,"vehicle_avail_pct":80,"storage_cold_facility":"Yes","digital_mis_pos":"Partial","quality_sop_score":68,"total_member_loans":5000000,"npa_member_loans":150000,"max_dpd_members":35,"restructured_loans_3yr":"Few Times","mgmt_experience":7,"internal_control_score":65,"loan_policy_compliance":"Yes","meeting_frequency":"Monthly","insurance_available":"Yes","regulatory_compliance":"Partial","climatic_risk_score":4,"credit_history_bfi":"Pass","max_dpd_bfi":0,"community_support_level":"Moderate","emergency_response":"Ad-hoc","farmer_training_freq":""}</t>
-  </si>
-  <si>
-    <t>2026-03-16T07:19:30.661Z</t>
-  </si>
-  <si>
-    <t>C Risk</t>
-  </si>
-  <si>
-    <t>Koshi Valley Cooperative (Test)</t>
-  </si>
-  <si>
-    <t>{"type_collection":"collection","type_processing":"processing","cust_new":"new","cust_existing":"existing","coop_name":"Koshi Valley Cooperative (Test)","model_type":"Milk Collection Only (Model A)","loan_type":"New Loan","years_operation":4,"office_location":"Morang, Koshi","existing_loan":1500000,"proposed_loan":5000000,"total_loan":6500000,"interest_rate":12,"loan_tenure":48,"installment_freq":"Quarterly","primary_land_value":5000000,"milk_sales":18000000,"other_product_sales":500000,"other_income":200000,"total_sales":18700000,"grant_income":2500000,"total_revenue":21200000,"bank_sales":9000000,"total_buyers":150,"top5_buyers_sales":10000000,"largest_buyer_sales":5000000,"top5_buyer_pct":53.5,"largest_buyer_pct":26.7,"avg_collection_days":55,"raw_milk_cost":13000000,"processing_cost":0,"packaging_cost":0,"transport_cost":400000,"other_processing_cost":0,"salary_expense":1200000,"admin_expense":350000,"electricity_expense":200000,"fuel_expense":150000,"repair_expense":100000,"rent_expense":80000,"other_opex":250000,"total_opex":15730000,"annual_depreciation":400000,"amortization_amount":30000,"cash_last_year":1500000,"cash_prev_year":1800000,"lowest_monthly_expense":400000,"income_expense_checked":"Occasionally","audit_observations":5,"avg_inventory_value":200000,"cash_hand":200000,"bank_balance":1300000,"total_cash":1500000,"accounts_receivable":1500000,"inventory_value":300000,"prepaid_expenses":50000,"other_current_assets":100000,"total_current_assets":3450000,"land_value":4000000,"building_value":1200000,"machinery_value":800000,"vehicle_value":600000,"furniture_value":150000,"other_fixed_assets":100000,"total_fixed_assets":6850000,"total_assets":10300000,"accounts_payable":800000,"short_term_loan":1500000,"accrued_expenses":300000,"current_ltd":1000000,"total_current_liabilities":3600000,"long_term_loan":4000000,"other_ltl":500000,"total_long_term_liabilities":4500000,"total_liabilities":8100000,"paid_up_capital":1500000,"retained_earnings":500000,"reserve_fund":300000,"total_net_worth":2300000,"total_milk_collected":1600000,"milk_loss":80000,"processing_loss":0,"total_milk_sold":1520000,"avg_monthly_milk":133000,"lowest_monthly_milk":80000,"collection_days":310,"total_farmers":280,"avg_milk_per_farmer":5714.3,"top5_farmers_milk":640000,"vehicle_avail_pct":60,"storage_cold_facility":"No","digital_mis_pos":"Partial","quality_sop_score":45,"total_member_loans":3500000,"npa_member_loans":280000,"max_dpd_members":65,"restructured_loans_3yr":"Few Times","mgmt_experience":4,"internal_control_score":45,"loan_policy_compliance":"No","meeting_frequency":"Monthly","insurance_available":"No","regulatory_compliance":"Partial","climatic_risk_score":6,"credit_history_bfi":"Watch List","max_dpd_bfi":10,"community_support_level":"Minimal","emergency_response":"Ad-hoc","farmer_training_freq":""}</t>
-  </si>
-  <si>
-    <t>2026-03-16T07:20:26.859Z</t>
-  </si>
-  <si>
-    <t>Failing Test Cooperative (Test)</t>
-  </si>
-  <si>
-    <t>{"type_collection":"collection","type_processing":"processing","cust_new":"new","cust_existing":"existing","coop_name":"Failing Test Cooperative (Test)","model_type":"Milk Collection Only (Model A)","loan_type":"New Loan","years_operation":1,"office_location":"Remote District","existing_loan":3000000,"proposed_loan":6000000,"total_loan":9000000,"interest_rate":16,"loan_tenure":36,"installment_freq":"Annual","primary_land_value":2000000,"milk_sales":8000000,"other_product_sales":0,"other_income":100000,"total_sales":8100000,"grant_income":5000000,"total_revenue":13100000,"bank_sales":2000000,"total_buyers":50,"top5_buyers_sales":6500000,"largest_buyer_sales":4000000,"top5_buyer_pct":80.2,"largest_buyer_pct":49.4,"avg_collection_days":90,"raw_milk_cost":7000000,"processing_cost":0,"packaging_cost":0,"transport_cost":300000,"other_processing_cost":0,"salary_expense":900000,"admin_expense":300000,"electricity_expense":150000,"fuel_expense":120000,"repair_expense":80000,"rent_expense":60000,"other_opex":200000,"total_opex":9110000,"annual_depreciation":200000,"amortization_amount":0,"cash_last_year":400000,"cash_prev_year":700000,"lowest_monthly_expense":700000,"income_expense_checked":"Never","audit_observations":10,"avg_inventory_value":100000,"cash_hand":50000,"bank_balance":350000,"total_cash":400000,"accounts_receivable":2500000,"inventory_value":150000,"prepaid_expenses":0,"other_current_assets":50000,"total_current_assets":3100000,"land_value":1800000,"building_value":600000,"machinery_value":400000,"vehicle_value":300000,"furniture_value":80000,"other_fixed_assets":50000,"total_fixed_assets":3230000,"total_assets":6330000,"accounts_payable":1500000,"short_term_loan":3000000,"accrued_expenses":600000,"current_ltd":1200000,"total_current_liabilities":6300000,"long_term_loan":4800000,"other_ltl":1000000,"total_long_term_liabilities":5800000,"total_liabilities":12100000,"paid_up_capital":500000,"retained_earnings":-200000,"reserve_fund":100000,"total_net_worth":400000,"total_milk_collected":700000,"milk_loss":70000,"processing_loss":0,"total_milk_sold":630000,"avg_monthly_milk":58000,"lowest_monthly_milk":20000,"collection_days":260,"total_farmers":90,"avg_milk_per_farmer":7777.8,"top5_farmers_milk":420000,"vehicle_avail_pct":40,"storage_cold_facility":"No","digital_mis_pos":"No","quality_sop_score":15,"total_member_loans":2000000,"npa_member_loans":600000,"max_dpd_members":120,"restructured_loans_3yr":"Frequently","mgmt_experience":1,"internal_control_score":20,"loan_policy_compliance":"No","meeting_frequency":"Rarely","insurance_available":"No","regulatory_compliance":"No","climatic_risk_score":9,"credit_history_bfi":"Substandard","max_dpd_bfi":45,"community_support_level":"Minimal","emergency_response":"No Plan","farmer_training_freq":""}</t>
-  </si>
-  <si>
-    <t>2026-03-16T07:39:34.265Z</t>
-  </si>
-  <si>
-    <t>2026-03-16T08:09:37.361Z</t>
-  </si>
-  <si>
-    <t>Test Coop</t>
-  </si>
-  <si>
-    <t>{"type_collection":"collection","type_processing":"processing","cust_new":"new","cust_existing":"existing","coop_name":"Test Coop","model_type":"Milk Collection Only (Model A)","loan_type":"New Loan","years_operation":10,"office_location":"","existing_loan":0,"proposed_loan":2000000,"total_loan":2000000,"interest_rate":0,"loan_tenure":0,"installment_freq":"Monthly","primary_land_value":0,"milk_sales":0,"other_product_sales":0,"other_income":0,"total_sales":0,"grant_income":0,"total_revenue":0,"bank_sales":0,"total_buyers":0,"top5_buyers_sales":0,"largest_buyer_sales":0,"top5_buyer_pct":0,"largest_buyer_pct":0,"avg_collection_days":0,"raw_milk_cost":0,"processing_cost":0,"packaging_cost":0,"transport_cost":0,"other_processing_cost":0,"salary_expense":0,"admin_expense":0,"electricity_expense":0,"fuel_expense":0,"repair_expense":0,"rent_expense":0,"other_opex":0,"total_opex":0,"annual_depreciation":0,"amortization_amount":0,"cash_last_year":0,"cash_prev_year":0,"lowest_monthly_expense":0,"income_expense_checked":"","audit_observations":0,"avg_inventory_value":0,"cash_hand":0,"bank_balance":0,"total_cash":0,"accounts_receivable":0,"inventory_value":0,"prepaid_expenses":0,"other_current_assets":0,"total_current_assets":0,"land_value":0,"building_value":0,"machinery_value":0,"vehicle_value":0,"furniture_value":0,"other_fixed_assets":0,"total_fixed_assets":0,"total_assets":0,"accounts_payable":0,"short_term_loan":0,"accrued_expenses":0,"current_ltd":0,"total_current_liabilities":0,"long_term_loan":0,"other_ltl":0,"total_long_term_liabilities":0,"total_liabilities":0,"paid_up_capital":0,"retained_earnings":0,"reserve_fund":0,"total_net_worth":0,"total_milk_collected":0,"milk_loss":0,"processing_loss":0,"total_milk_sold":0,"avg_monthly_milk":0,"lowest_monthly_milk":0,"collection_days":0,"total_farmers":0,"avg_milk_per_farmer":0,"top5_farmers_milk":0,"vehicle_avail_pct":0,"storage_cold_facility":"","digital_mis_pos":"","quality_sop_score":0,"total_member_loans":0,"npa_member_loans":0,"max_dpd_members":0,"restructured_loans_3yr":"","mgmt_experience":0,"internal_control_score":0,"loan_policy_compliance":"","meeting_frequency":"","insurance_available":"","regulatory_compliance":"","climatic_risk_score":0,"credit_history_bfi":"","max_dpd_bfi":0,"community_support_level":"","emergency_response":"","farmer_training_freq":""}</t>
-  </si>
-  <si>
-    <t>2026-03-16T09:23:26.768Z</t>
-  </si>
-  <si>
-    <t>{"type_collection":"collection","type_processing":"processing","cust_new":"new","cust_existing":"existing","coop_name":"Koshi Valley Cooperative (Test)","model_type":"Milk Collection Only (Model A)","loan_type":"New Loan","years_operation":4,"office_location":"Morang, Koshi","existing_loan":1500000,"proposed_loan":5000000,"total_loan":6500000,"interest_rate":12,"loan_tenure":48,"installment_freq":"Quarterly","primary_land_value":5000000,"milk_sales":18000000,"other_product_sales":500000,"other_income":200000,"total_sales":18700000,"grant_income":2500000,"total_revenue":21200000,"bank_sales":9000000,"total_buyers":150,"top5_buyers_sales":10000000,"largest_buyer_sales":5000000,"top5_buyer_pct":53.5,"largest_buyer_pct":26.7,"avg_collection_days":55,"raw_milk_cost":13000000,"processing_cost":0,"packaging_cost":0,"transport_cost":400000,"other_processing_cost":0,"salary_expense":1200000,"admin_expense":350000,"electricity_expense":200000,"fuel_expense":150000,"repair_expense":100000,"rent_expense":80000,"other_opex":250000,"total_opex":15730000,"annual_depreciation":400000,"amortization_amount":30000,"cash_last_year":1500000,"cash_prev_year":1800000,"lowest_monthly_expense":400000,"income_expense_checked":"Occasionally","audit_observations":5,"avg_inventory_value":200000,"cash_hand":200000,"bank_balance":1300000,"total_cash":1500000,"accounts_receivable":1500000,"inventory_value":300000,"prepaid_expenses":50000,"other_current_assets":100000,"total_current_assets":3450000,"land_value":4000000,"building_value":1200000,"machinery_value":800000,"vehicle_value":600000,"furniture_value":150000,"other_fixed_assets":100000,"total_fixed_assets":6850000,"total_assets":10300000,"accounts_payable":800000,"short_term_loan":1500000,"accrued_expenses":300000,"current_ltd":1000000,"total_current_liabilities":3600000,"long_term_loan":4000000,"other_ltl":500000,"total_long_term_liabilities":4500000,"total_liabilities":8100000,"paid_up_capital":1500000,"retained_earnings":500000,"reserve_fund":300000,"total_net_worth":2300000,"total_milk_collected":1600000,"milk_loss":80000,"processing_loss":0,"total_milk_sold":1520000,"avg_monthly_milk":133000,"lowest_monthly_milk":80000,"collection_days":310,"total_farmers":280,"avg_milk_per_farmer":5714.3,"top5_farmers_milk":640000,"vehicle_avail_pct":60,"storage_cold_facility":"No","digital_mis_pos":"Partial","quality_sop_score":45,"total_member_loans":3500000,"npa_member_loans":280000,"max_dpd_members":65,"restructured_loans_3yr":"Few Times","mgmt_experience":4,"internal_control_score":45,"loan_policy_compliance":"No","meeting_frequency":"Monthly","insurance_available":"No","regulatory_compliance":"Partial","climatic_risk_score":6,"credit_history_bfi":"Watch List","max_dpd_bfi":10,"community_support_level":"Minimal","emergency_response":"Ad-hoc","farmer_training_freq":"","customer_type":"new"}</t>
-  </si>
-  <si>
-    <t>2026-03-16T09:31:57.624Z</t>
-  </si>
-  <si>
-    <t>Failing Test (Test)</t>
-  </si>
-  <si>
-    <t>{"type_collection":"collection","type_processing":"processing","cust_new":"new","cust_existing":"existing","coop_name":"Failing Test (Test)","model_type":"Collection &amp; Processing (Model B)","loan_type":"New Loan","years_operation":1,"office_location":"Remote District","existing_loan":3000000,"proposed_loan":6000000,"total_loan":9000000,"interest_rate":16,"loan_tenure":36,"installment_freq":"Annual","primary_land_value":2000000,"milk_sales":8000000,"other_product_sales":0,"other_income":100000,"total_sales":8100000,"grant_income":5000000,"total_revenue":13100000,"bank_sales":2000000,"total_buyers":50,"top5_buyers_sales":6500000,"largest_buyer_sales":4000000,"top5_buyer_pct":80.2,"largest_buyer_pct":49.4,"avg_collection_days":90,"raw_milk_cost":7000000,"processing_cost":0,"packaging_cost":0,"transport_cost":300000,"other_processing_cost":0,"salary_expense":900000,"admin_expense":300000,"electricity_expense":150000,"fuel_expense":120000,"repair_expense":80000,"rent_expense":60000,"other_opex":200000,"total_opex":9110000,"annual_depreciation":200000,"amortization_amount":0,"cash_last_year":400000,"cash_prev_year":700000,"lowest_monthly_expense":700000,"income_expense_checked":"Never","audit_observations":10,"avg_inventory_value":100000,"cash_hand":50000,"bank_balance":350000,"total_cash":400000,"accounts_receivable":2500000,"inventory_value":150000,"prepaid_expenses":0,"other_current_assets":50000,"total_current_assets":3100000,"land_value":1800000,"building_value":600000,"machinery_value":400000,"vehicle_value":300000,"furniture_value":80000,"other_fixed_assets":50000,"total_fixed_assets":3230000,"total_assets":6330000,"accounts_payable":1500000,"short_term_loan":3000000,"accrued_expenses":600000,"current_ltd":1200000,"total_current_liabilities":6300000,"long_term_loan":4800000,"other_ltl":1000000,"total_long_term_liabilities":5800000,"total_liabilities":12100000,"paid_up_capital":500000,"retained_earnings":-200000,"reserve_fund":100000,"total_net_worth":400000,"total_milk_collected":700000,"milk_loss":70000,"processing_loss":0,"total_milk_sold":630000,"avg_monthly_milk":58000,"lowest_monthly_milk":20000,"collection_days":260,"total_farmers":90,"avg_milk_per_farmer":7777.8,"top5_farmers_milk":420000,"vehicle_avail_pct":40,"storage_cold_facility":"No","digital_mis_pos":"No","quality_sop_score":15,"total_member_loans":2000000,"npa_member_loans":600000,"max_dpd_members":120,"restructured_loans_3yr":"Frequently","mgmt_experience":1,"internal_control_score":20,"loan_policy_compliance":"No","meeting_frequency":"Rarely","insurance_available":"No","regulatory_compliance":"No","climatic_risk_score":9,"credit_history_bfi":"Substandard","max_dpd_bfi":45,"community_support_level":"Minimal","emergency_response":"No Plan","farmer_training_freq":"","customer_type":"new"}</t>
+    <t>{"model_type":"","loan_type":"","coop_name":"Terai Milk Cooperative (Test)","years_operation":8,"office_location":"Chitwan, Bagmati","total_loan":"4500000","existing_loan":500000,"proposed_loan":4000000,"interest_rate":10,"loan_tenure":60,"installment_freq":"Monthly","primary_land_value":7000000,"total_sales":"31800000","total_revenue":"32600000","milk_sales":30000000,"other_product_sales":1500000,"other_income":300000,"grant_income":800000,"bank_sales":22000000,"top5_buyer_pct":"37.74","largest_buyer_pct":"12.58","total_buyers":300,"top5_buyers_sales":12000000,"largest_buyer_sales":4000000,"gov_buyer_sales":5000000,"no_govt_buyers":2,"large_private_buyer_sales":15000000,"no_private_sector_buyer":4,"small_buyer_sales":800000,"no_small_buyer_sales":8,"avg_collection_days":35,"contract_coverage":5,"total_opex":"23350000","raw_milk_cost":20000000,"processing_cost":0,"packaging_cost":0,"transport_cost":500000,"other_processing_cost":0,"salary_expense":1500000,"admin_expense":400000,"electricity_expense":250000,"fuel_expense":180000,"repair_expense":120000,"rent_expense":100000,"other_opex":300000,"lowest_monthly_expense":300000,"annual_depreciation":600000,"amortization_amount":50000,"total_cash":"3200000","total_current_assets":"4830000","total_fixed_assets":"11050000","total_assets":"15880000","cash_hand":300000,"bank_balance":2900000,"accounts_receivable":1000000,"inventory_value":400000,"prepaid_expenses":80000,"other_current_assets":150000,"land_value":6000000,"building_value":2000000,"machinery_value":1500000,"vehicle_value":1200000,"furniture_value":200000,"other_fixed_assets":150000,"total_current_liabilities":"1950000","total_long_term_liabilities":"3200000","total_liabilities":"5150000","accounts_payable":500000,"short_term_loan":500000,"accrued_expenses":150000,"current_ltd":800000,"long_term_loan":3200000,"other_ltl":0,"total_net_worth":"6000000","paid_up_capital":3000000,"retained_earnings":2000000,"reserve_fund":1000000,"total_milk_sold":"2730000","avg_milk_per_farmer":"6222.22","total_milk_collected":2800000,"milk_loss":70000,"processing_loss":0,"avg_monthly_milk":233000,"lowest_monthly_milk":180000,"highest_monthly_milk":290000,"avg_inventory_value":300000,"credit_period_given_days":10,"top5_farmers_milk":560000,"highest_farmer_qty":70000,"lowest_farmer_qty":800,"total_farmers":450,"collection_days":340,"total_member_loans":5000000,"npa_member_loans":150000,"overdue_member_loans":200000,"restructured_loans_3yr":"Few Times","max_dpd_members":35,"credit_history_flag":"With few delays","cash_last_year":3200000,"cash_prev_year":2800000,"audit_observations":2,"mgmt_experience":7,"internal_control_score":"65","loan_policy_compliance":"Yes","vehicle_avail_pct":"Yes","storage_cold_facility":"Yes","quality_sop_score":"65","insurance_available":"Yes","digital_mis_pos":"Partial","regulatory_compliance":"Partial","climatic_risk_score":"5","credit_history_bfi":"Pass","max_dpd_bfi":0,"meeting_frequency":"Monthly","member_info_transparency":"Mostly","fund_usage":"Buying Milk","kyc_aml":"Mostly","income_expense_checked":"Regularly","right_to_information":"Mostly Beforehand","community_support_level":"Moderate","emergency_response":"Ad-hoc","customer_type":"new"}</t>
+  </si>
+  <si>
+    <t>SUB-1482A024-26D</t>
+  </si>
+  <si>
+    <t>conditional</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>2026-03-18T05:05:13.624Z</t>
+  </si>
+  <si>
+    <t>2026-03-18T05:08:06.634Z</t>
+  </si>
+  <si>
+    <t>SUB-3ED24871-3F0</t>
+  </si>
+  <si>
+    <t>2026-03-18T05:23:51.302Z</t>
+  </si>
+  <si>
+    <t>SUB-5BDCEB7B-D20</t>
+  </si>
+  <si>
+    <t>2026-03-18T05:39:41.105Z</t>
+  </si>
+  <si>
+    <t>Manual testing</t>
+  </si>
+  <si>
+    <t>{"model_type":"","loan_type":"","coop_name":"Manual testing","years_operation":5,"office_location":"Chitwan, Bagmati","total_loan":"148530482","existing_loan":148484848,"proposed_loan":45634,"interest_rate":45,"loan_tenure":53,"installment_freq":"Quarterly","primary_land_value":453453453,"total_sales":"1360360359","total_revenue":"1360813812","milk_sales":453453453,"other_product_sales":453453453,"other_income":453453453,"grant_income":453453,"bank_sales":453453453453,"top5_buyer_pct":"33333.33","largest_buyer_pct":"39.95","total_buyers":453,"top5_buyers_sales":453453453453,"largest_buyer_sales":543453453,"gov_buyer_sales":453453453,"no_govt_buyers":4,"large_private_buyer_sales":453453453,"no_private_sector_buyer":4,"small_buyer_sales":453453453,"no_small_buyer_sales":54,"avg_collection_days":45,"contract_coverage":5,"total_opex":"11999162158","raw_milk_cost":4563453453,"processing_cost":0,"packaging_cost":0,"transport_cost":4534534534,"other_processing_cost":0,"salary_expense":543453453,"admin_expense":543453453,"electricity_expense":453453453,"fuel_expense":453453453,"repair_expense":453453453,"rent_expense":453453,"other_opex":453453453,"lowest_monthly_expense":543453453,"annual_depreciation":453453,"amortization_amount":4,"total_cash":"45796887","total_current_assets":"141495362","total_fixed_assets":"5751094482","total_assets":"5892589844","cash_hand":453453,"bank_balance":45343434,"accounts_receivable":4554354,"inventory_value":45345345,"prepaid_expenses":453433,"other_current_assets":45345343,"land_value":453453453,"building_value":45343435,"machinery_value":4345345344,"vehicle_value":453453453,"furniture_value":453453453,"other_fixed_assets":45344,"total_current_liabilities":"1903813812","total_long_term_liabilities":"453453457","total_liabilities":"2357267269","accounts_payable":453453453,"short_term_loan":453453453,"accrued_expenses":543453453,"current_ltd":453453453,"long_term_loan":453453453,"other_ltl":4,"total_net_worth":"1360360359","paid_up_capital":453453453,"retained_earnings":453453453,"reserve_fund":453453453,"total_milk_sold":"400000000","avg_milk_per_farmer":"1001001","total_milk_collected":453453453,"milk_loss":53453453,"processing_loss":0,"avg_monthly_milk":453453435,"lowest_monthly_milk":45345343,"highest_monthly_milk":453453453,"avg_inventory_value":453453453,"credit_period_given_days":45,"top5_farmers_milk":453453453,"highest_farmer_qty":453453453,"lowest_farmer_qty":453,"total_farmers":453,"collection_days":453,"total_member_loans":45343435545,"npa_member_loans":5434534,"overdue_member_loans":453453453,"restructured_loans_3yr":"Few Times","max_dpd_members":45,"credit_history_flag":"With few delays","cash_last_year":453453453,"cash_prev_year":453453453,"audit_observations":5,"mgmt_experience":8,"internal_control_score":"65","loan_policy_compliance":"Yes","vehicle_avail_pct":"Yes","storage_cold_facility":"Yes","quality_sop_score":"85","insurance_available":"Yes","digital_mis_pos":"Partial","regulatory_compliance":"Partial","climatic_risk_score":"5","credit_history_bfi":"Substandard","max_dpd_bfi":4,"meeting_frequency":"Monthly","member_info_transparency":"Sometimes","fund_usage":"Processing","kyc_aml":"Sometimes","income_expense_checked":"Occasionally","right_to_information":"Mostly Beforehand","community_support_level":"Moderate","emergency_response":"Ad-hoc","customer_type":"new"}</t>
+  </si>
+  <si>
+    <t>SUB-4E8ECBC2-948</t>
+  </si>
+  <si>
+    <t>2026-03-18T05:47:44.817Z</t>
+  </si>
+  <si>
+    <t>SUB-42357BCB-832</t>
   </si>
   <si>
     <t>Email</t>
@@ -1599,12 +1650,6 @@
   </si>
   <si>
     <t>Result</t>
-  </si>
-  <si>
-    <t>Dummy Test Cooperative</t>
-  </si>
-  <si>
-    <t>{"totalScore":784,"rawTotal":784,"rawMax":1000,"riskCategory":"A RISK","logs":[{"name":"DSCR","value":"36","score":36,"max":60,"category":"Cash Flow &amp; Loan Repayment","dataValue":36},{"name":"Seasonality Coverage","value":"30","score":30,"max":50,"category":"Cash Flow &amp; Loan Repayment","dataValue":30},{"name":"Inventory Days","value":"30","score":30,"max":30,"category":"Cash Flow &amp; Loan Repayment","dataValue":30},{"name":"Receivable Days","value":"40","score":40,"max":40,"category":"Cash Flow &amp; Loan Repayment","dataValue":40},{"name":"Milk Stability %","value":"18","score":18,"max":30,"category":"Milk Supply &amp; Operational Stability","dataValue":18},{"name":"Days Stability %","value":"15","score":15,"max":20,"category":"Milk Supply &amp; Operational Stability","dataValue":15},{"name":"Milk Loss %","value":"20","score":20,"max":20,"category":"Milk Supply &amp; Operational Stability","dataValue":20},{"name":"Yield Loss %","value":"20","score":20,"max":20,"category":"Milk Supply &amp; Operational Stability","dataValue":20},{"name":"Farmer Concentration %","value":"15","score":15,"max":15,"category":"Milk Supply &amp; Operational Stability","dataValue":15},{"name":"Collection Stability %","value":"4","score":4,"max":15,"category":"Milk Supply &amp; Operational Stability","dataValue":4},{"name":"Payment Fairness %","value":"4","score":4,"max":15,"category":"Milk Supply &amp; Operational Stability","dataValue":4},{"name":"Logistics Reliability","value":"15","score":15,"max":15,"category":"Milk Supply &amp; Operational Stability","dataValue":15},{"name":"Net Worth","value":"40","score":40,"max":40,"category":"Financial Strength &amp; Liquidity","dataValue":40},{"name":"Debt / Equity","value":"32","score":32,"max":40,"category":"Financial Strength &amp; Liquidity","dataValue":32},{"name":"Current Ratio","value":"40","score":40,"max":40,"category":"Financial Strength &amp; Liquidity","dataValue":40},{"name":"Grant % of Revenue","value":"30","score":30,"max":30,"category":"Financial Strength &amp; Liquidity","dataValue":30},{"name":"Cash / Bank Balance Trend","value":"30","score":30,"max":30,"category":"Financial Strength &amp; Liquidity","dataValue":30},{"name":"% Sales via Bank","value":"25","score":25,"max":25,"category":"Financial Transparency &amp; Cash Discipline","dataValue":25},{"name":"Digital MIS / POS / QR Adoption","value":"25","score":25,"max":25,"category":"Financial Transparency &amp; Cash Discipline","dataValue":25},{"name":"Member GNPA %","value":"15","score":15,"max":45,"category":"Loan Recovery &amp; Member Credit Risk","dataValue":15},{"name":"Max DPD","value":"15","score":15,"max":35,"category":"Loan Recovery &amp; Member Credit Risk","dataValue":15},{"name":"Restructuring","value":"15","score":15,"max":20,"category":"Loan Recovery &amp; Member Credit Risk","dataValue":15},{"name":"Management Experience","value":"15","score":15,"max":25,"category":"Management &amp; Governance Quality","dataValue":15},{"name":"Internal Controls","value":"25","score":25,"max":25,"category":"Management &amp; Governance Quality","dataValue":25},{"name":"Audit Findings","value":"15","score":15,"max":25,"category":"Management &amp; Governance Quality","dataValue":15},{"name":"Lending Policy Compliance","value":"25","score":25,"max":25,"category":"Management &amp; Governance Quality","dataValue":25},{"name":"Quality SOP Compliance","value":"40","score":40,"max":40,"category":"Operational Quality","dataValue":40},{"name":"Insurance Coverage","value":"10","score":10,"max":10,"category":"External &amp; Regulatory Risk","dataValue":10},{"name":"Regulatory Compliance","value":"5","score":5,"max":15,"category":"External &amp; Regulatory Risk","dataValue":5},{"name":"Climatic Risk","value":"0","score":0,"max":15,"category":"External &amp; Regulatory Risk","dataValue":0},{"name":"Credit History","value":"20","score":20,"max":20,"category":"Credit History / Banking Behaviour","dataValue":20},{"name":"Max Delays","value":"20","score":20,"max":20,"category":"Credit History / Banking Behaviour","dataValue":20},{"name":"Top 5 Buyer Concentration %","value":"20","score":20,"max":25,"category":"Buyer Concentration &amp; Market Risk","dataValue":20},{"name":"Largest Buyer Concentration %","value":"25","score":25,"max":25,"category":"Buyer Concentration &amp; Market Risk","dataValue":25},{"name":"Stable Buyer Share %","value":"5","score":5,"max":10,"category":"Buyer Concentration &amp; Market Risk","dataValue":5},{"name":"Contract Coverage %","value":"5","score":5,"max":10,"category":"Buyer Concentration &amp; Market Risk","dataValue":5},{"name":"Payment Score","value":"0","score":0,"max":10,"category":"Buyer Concentration &amp; Market Risk","dataValue":10},{"name":"Committee Meeting Frequency","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Member Info Transparency","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Fund Utilization Transparency","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Member Identification &amp; KYC Compliance","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Financial Oversight &amp; Verification Practice","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Governance Communication Effectiveness","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Stakeholder Engagement &amp; Social Responsibility","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Operational Contingency Preparedness","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5}],"categories":[{"name":"Cash Flow &amp; Loan Repayment","max":180,"score":136,"logs":[{"name":"DSCR","value":"36","score":36,"max":60,"category":"Cash Flow &amp; Loan Repayment","dataValue":36},{"name":"Seasonality Coverage","value":"30","score":30,"max":50,"category":"Cash Flow &amp; Loan Repayment","dataValue":30},{"name":"Inventory Days","value":"30","score":30,"max":30,"category":"Cash Flow &amp; Loan Repayment","dataValue":30},{"name":"Receivable Days","value":"40","score":40,"max":40,"category":"Cash Flow &amp; Loan Repayment","dataValue":40}]},{"name":"Milk Supply &amp; Operational Stability","max":150,"score":111,"logs":[{"name":"Milk Stability %","value":"18","score":18,"max":30,"category":"Milk Supply &amp; Operational Stability","dataValue":18},{"name":"Days Stability %","value":"15","score":15,"max":20,"category":"Milk Supply &amp; Operational Stability","dataValue":15},{"name":"Milk Loss %","value":"20","score":20,"max":20,"category":"Milk Supply &amp; Operational Stability","dataValue":20},{"name":"Yield Loss %","value":"20","score":20,"max":20,"category":"Milk Supply &amp; Operational Stability","dataValue":20},{"name":"Farmer Concentration %","value":"15","score":15,"max":15,"category":"Milk Supply &amp; Operational Stability","dataValue":15},{"name":"Collection Stability %","value":"4","score":4,"max":15,"category":"Milk Supply &amp; Operational Stability","dataValue":4},{"name":"Payment Fairness %","value":"4","score":4,"max":15,"category":"Milk Supply &amp; Operational Stability","dataValue":4},{"name":"Logistics Reliability","value":"15","score":15,"max":15,"category":"Milk Supply &amp; Operational Stability","dataValue":15}]},{"name":"Financial Strength &amp; Liquidity","max":180,"score":172,"logs":[{"name":"Net Worth","value":"40","score":40,"max":40,"category":"Financial Strength &amp; Liquidity","dataValue":40},{"name":"Debt / Equity","value":"32","score":32,"max":40,"category":"Financial Strength &amp; Liquidity","dataValue":32},{"name":"Current Ratio","value":"40","score":40,"max":40,"category":"Financial Strength &amp; Liquidity","dataValue":40},{"name":"Grant % of Revenue","value":"30","score":30,"max":30,"category":"Financial Strength &amp; Liquidity","dataValue":30},{"name":"Cash / Bank Balance Trend","value":"30","score":30,"max":30,"category":"Financial Strength &amp; Liquidity","dataValue":30}]},{"name":"Financial Transparency &amp; Cash Discipline","max":50,"score":50,"logs":[{"name":"% Sales via Bank","value":"25","score":25,"max":25,"category":"Financial Transparency &amp; Cash Discipline","dataValue":25},{"name":"Digital MIS / POS / QR Adoption","value":"25","score":25,"max":25,"category":"Financial Transparency &amp; Cash Discipline","dataValue":25}]},{"name":"Loan Recovery &amp; Member Credit Risk","max":100,"score":45,"logs":[{"name":"Member GNPA %","value":"15","score":15,"max":45,"category":"Loan Recovery &amp; Member Credit Risk","dataValue":15},{"name":"Max DPD","value":"15","score":15,"max":35,"category":"Loan Recovery &amp; Member Credit Risk","dataValue":15},{"name":"Restructuring","value":"15","score":15,"max":20,"category":"Loan Recovery &amp; Member Credit Risk","dataValue":15}]},{"name":"Management &amp; Governance Quality","max":100,"score":80,"logs":[{"name":"Management Experience","value":"15","score":15,"max":25,"category":"Management &amp; Governance Quality","dataValue":15},{"name":"Internal Controls","value":"25","score":25,"max":25,"category":"Management &amp; Governance Quality","dataValue":25},{"name":"Audit Findings","value":"15","score":15,"max":25,"category":"Management &amp; Governance Quality","dataValue":15},{"name":"Lending Policy Compliance","value":"25","score":25,"max":25,"category":"Management &amp; Governance Quality","dataValue":25}]},{"name":"Operational Quality","max":40,"score":40,"logs":[{"name":"Quality SOP Compliance","value":"40","score":40,"max":40,"category":"Operational Quality","dataValue":40}]},{"name":"External &amp; Regulatory Risk","max":40,"score":15,"logs":[{"name":"Insurance Coverage","value":"10","score":10,"max":10,"category":"External &amp; Regulatory Risk","dataValue":10},{"name":"Regulatory Compliance","value":"5","score":5,"max":15,"category":"External &amp; Regulatory Risk","dataValue":5},{"name":"Climatic Risk","value":"0","score":0,"max":15,"category":"External &amp; Regulatory Risk","dataValue":0}]},{"name":"Credit History / Banking Behaviour","max":40,"score":40,"logs":[{"name":"Credit History","value":"20","score":20,"max":20,"category":"Credit History / Banking Behaviour","dataValue":20},{"name":"Max Delays","value":"20","score":20,"max":20,"category":"Credit History / Banking Behaviour","dataValue":20}]},{"name":"Buyer Concentration &amp; Market Risk","max":80,"score":55,"logs":[{"name":"Top 5 Buyer Concentration %","value":"20","score":20,"max":25,"category":"Buyer Concentration &amp; Market Risk","dataValue":20},{"name":"Largest Buyer Concentration %","value":"25","score":25,"max":25,"category":"Buyer Concentration &amp; Market Risk","dataValue":25},{"name":"Stable Buyer Share %","value":"5","score":5,"max":10,"category":"Buyer Concentration &amp; Market Risk","dataValue":5},{"name":"Contract Coverage %","value":"5","score":5,"max":10,"category":"Buyer Concentration &amp; Market Risk","dataValue":5},{"name":"Payment Score","value":"0","score":0,"max":10,"category":"Buyer Concentration &amp; Market Risk","dataValue":10}]},{"name":"Behavioural &amp; Due Diligence Risk","max":40,"score":40,"logs":[{"name":"Committee Meeting Frequency","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Member Info Transparency","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Fund Utilization Transparency","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Member Identification &amp; KYC Compliance","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Financial Oversight &amp; Verification Practice","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Governance Communication Effectiveness","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Stakeholder Engagement &amp; Social Responsibility","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5},{"name":"Operational Contingency Preparedness","value":"5","score":5,"max":5,"category":"Behavioural &amp; Due Diligence Risk","dataValue":5}]}],"strengths":["Strong performance in &lt;strong&gt;Financial Strength &amp; Liquidity&lt;/strong&gt; (96%) — 172/180 pts","Strong performance in &lt;strong&gt;Financial Transparency &amp; Cash Discipline&lt;/strong&gt; (100%) — 50/50 pts","Strong performance in &lt;strong&gt;Management &amp; Governance Quality&lt;/strong&gt; (80%) — 80/100 pts","Strong performance in &lt;strong&gt;Operational Quality&lt;/strong&gt; (100%) — 40/40 pts","Strong performance in &lt;strong&gt;Credit History / Banking Behaviour&lt;/strong&gt; (100%) — 40/40 pts","Strong performance in &lt;strong&gt;Behavioural &amp; Due Diligence Risk&lt;/strong&gt; (100%) — 40/40 pts"],"weaknesses":["Low score in &lt;strong&gt;External &amp; Regulatory Risk&lt;/strong&gt; (38%) — 15/40 pts requires immediate attention"],"focus":["Moderate score in &lt;strong&gt;Cash Flow &amp; Loan Repayment&lt;/strong&gt; (76%) — review sub-indicators for quick gains","Moderate score in &lt;strong&gt;Milk Supply &amp; Operational Stability&lt;/strong&gt; (74%) — review sub-indicators for quick gains","Priority improvement needed in &lt;strong&gt;External &amp; Regulatory Risk&lt;/strong&gt; (15/40 pts)","Moderate score in &lt;strong&gt;Buyer Concentration &amp; Market Risk&lt;/strong&gt; (69%) — review sub-indicators for quick gains"],"recommendation":"A score of 784/1,000 indicates &lt;strong&gt;good creditworthiness&lt;/strong&gt;. This cooperative demonstrates solid financial management and operational capacity. Loan approval at standard terms is recommended. Continue monitoring &lt;strong&gt;External &amp; Regulatory Risk&lt;/strong&gt;. Annual review is sufficient.","metrics":{"dscr":36,"debtEquity":32,"ebitda":0,"debtService":0,"seasonBuffer":30,"top5Buyers":20,"singleBuyer":0,"govtLargePvt":5},"heatmap":{"repayment":76,"operational":74,"financial":96,"governance":80}}</t>
   </si>
 </sst>
 </file>
@@ -1780,7 +1825,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2041,6 +2086,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="14" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -11771,7 +11819,11 @@
     <col customWidth="1" min="1" max="1" width="22.88"/>
     <col customWidth="1" min="2" max="2" width="20.25"/>
     <col customWidth="1" min="5" max="5" width="43.0"/>
-    <col customWidth="1" min="6" max="6" width="93.75"/>
+    <col customWidth="1" min="6" max="6" width="116.88"/>
+    <col customWidth="1" min="7" max="7" width="24.75"/>
+    <col customWidth="1" min="8" max="8" width="14.88"/>
+    <col customWidth="1" min="9" max="9" width="14.63"/>
+    <col customWidth="1" min="10" max="10" width="21.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11793,186 +11845,291 @@
       <c r="F1" s="91" t="s">
         <v>486</v>
       </c>
+      <c r="G1" s="91" t="s">
+        <v>487</v>
+      </c>
+      <c r="H1" s="91" t="s">
+        <v>488</v>
+      </c>
+      <c r="I1" s="91" t="s">
+        <v>489</v>
+      </c>
+      <c r="J1" s="91" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="91" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B2" s="92">
-        <v>46097.53850430556</v>
+        <v>46099.39951693287</v>
       </c>
       <c r="C2" s="93">
-        <v>448.0</v>
+        <v>299.0</v>
       </c>
       <c r="D2" s="91" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E2" s="91" t="s">
-        <v>5</v>
+        <v>493</v>
       </c>
       <c r="F2" s="91" t="s">
-        <v>489</v>
+        <v>494</v>
+      </c>
+      <c r="G2" s="91" t="s">
+        <v>495</v>
+      </c>
+      <c r="H2" s="91" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="91" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B3" s="92">
-        <v>46097.54399996527</v>
+        <v>46099.402165590276</v>
       </c>
       <c r="C3" s="93">
-        <v>907.0</v>
+        <v>900.0</v>
       </c>
       <c r="D3" s="91" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="E3" s="91" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="F3" s="91" t="s">
-        <v>493</v>
+        <v>500</v>
+      </c>
+      <c r="G3" s="91" t="s">
+        <v>501</v>
+      </c>
+      <c r="H3" s="91" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="91" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B4" s="92">
-        <v>46097.54452888889</v>
+        <v>46099.42030346065</v>
       </c>
       <c r="C4" s="93">
-        <v>756.0</v>
+        <v>900.0</v>
       </c>
       <c r="D4" s="91" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E4" s="91" t="s">
+        <v>499</v>
+      </c>
+      <c r="F4" s="91" t="s">
+        <v>503</v>
+      </c>
+      <c r="G4" s="91" t="s">
+        <v>504</v>
+      </c>
+      <c r="H4" s="91" t="s">
         <v>496</v>
-      </c>
-      <c r="F4" s="91" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="91" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B5" s="92">
-        <v>46097.54476387732</v>
+        <v>46099.43085444444</v>
       </c>
       <c r="C5" s="93">
-        <v>504.0</v>
+        <v>519.0</v>
       </c>
       <c r="D5" s="91" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="E5" s="91" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="F5" s="91" t="s">
-        <v>501</v>
+        <v>508</v>
+      </c>
+      <c r="G5" s="91" t="s">
+        <v>509</v>
+      </c>
+      <c r="H5" s="91" t="s">
+        <v>510</v>
+      </c>
+      <c r="I5" s="91" t="s">
+        <v>511</v>
+      </c>
+      <c r="J5" s="91" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="91" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B6" s="92">
-        <v>46097.5454131713</v>
+        <v>46099.43217667824</v>
       </c>
       <c r="C6" s="93">
-        <v>271.0</v>
+        <v>749.0</v>
       </c>
       <c r="D6" s="91" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="E6" s="91" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="F6" s="91" t="s">
-        <v>504</v>
+        <v>516</v>
+      </c>
+      <c r="G6" s="91" t="s">
+        <v>517</v>
+      </c>
+      <c r="H6" s="91" t="s">
+        <v>518</v>
+      </c>
+      <c r="I6" s="91" t="s">
+        <v>519</v>
+      </c>
+      <c r="J6" s="91" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="91" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="B7" s="92">
-        <v>46097.55869664352</v>
+        <v>46099.453558912035</v>
       </c>
       <c r="C7" s="93">
-        <v>504.0</v>
+        <v>749.0</v>
       </c>
       <c r="D7" s="91" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="E7" s="91" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="F7" s="91" t="s">
-        <v>501</v>
+        <v>516</v>
+      </c>
+      <c r="G7" s="91" t="s">
+        <v>522</v>
+      </c>
+      <c r="H7" s="91" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="91" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
       <c r="B8" s="92">
-        <v>46097.57956780093</v>
+        <v>46099.464488530095</v>
       </c>
       <c r="C8" s="93">
-        <v>465.0</v>
+        <v>900.0</v>
       </c>
       <c r="D8" s="91" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="E8" s="91" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="F8" s="91" t="s">
-        <v>508</v>
+        <v>500</v>
+      </c>
+      <c r="G8" s="91" t="s">
+        <v>524</v>
+      </c>
+      <c r="H8" s="91" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="91" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="B9" s="92">
-        <v>46097.630842928236</v>
+        <v>46099.475507986106</v>
       </c>
       <c r="C9" s="93">
-        <v>520.0</v>
+        <v>614.0</v>
       </c>
       <c r="D9" s="91" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="E9" s="91" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="F9" s="91" t="s">
-        <v>510</v>
+        <v>527</v>
+      </c>
+      <c r="G9" s="91" t="s">
+        <v>528</v>
+      </c>
+      <c r="H9" s="91" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="91" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="B10" s="92">
-        <v>46097.6367478125</v>
+        <v>46099.48110961806</v>
       </c>
       <c r="C10" s="93">
-        <v>299.0</v>
+        <v>900.0</v>
       </c>
       <c r="D10" s="91" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="E10" s="91" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="F10" s="91" t="s">
-        <v>513</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="G10" s="91" t="s">
+        <v>530</v>
+      </c>
+      <c r="H10" s="91" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="92"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="92"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="92"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="92"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="92"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="92"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="92"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="92"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="92"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -11996,36 +12153,62 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="91" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="B1" s="91" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="C1" s="91" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="D1" s="91" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="E1" s="91" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="F1" s="91" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="91" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="B2" s="91" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="C2" s="91" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="D2" s="91" t="s">
-        <v>523</v>
+        <v>540</v>
+      </c>
+      <c r="E2" s="94">
+        <v>46099.46475119213</v>
+      </c>
+      <c r="F2" s="94">
+        <v>46099.33655222222</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="91" t="s">
+        <v>519</v>
+      </c>
+      <c r="B3" s="91" t="s">
+        <v>538</v>
+      </c>
+      <c r="C3" s="91" t="s">
+        <v>539</v>
+      </c>
+      <c r="D3" s="91" t="s">
+        <v>540</v>
+      </c>
+      <c r="E3" s="94">
+        <v>46099.47625128472</v>
+      </c>
+      <c r="F3" s="94">
+        <v>46098.438512962966</v>
       </c>
     </row>
   </sheetData>
@@ -12047,32 +12230,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="94" t="s">
-        <v>524</v>
-      </c>
-      <c r="B1" s="95" t="s">
+      <c r="A1" s="95" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="94" t="s">
-        <v>525</v>
-      </c>
-      <c r="D1" s="94" t="s">
-        <v>526</v>
+      <c r="C1" s="95" t="s">
+        <v>542</v>
+      </c>
+      <c r="D1" s="95" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="93">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="91" t="s">
-        <v>527</v>
-      </c>
-      <c r="C2" s="92">
-        <v>46097.64362556713</v>
-      </c>
-      <c r="D2" s="91" t="s">
-        <v>528</v>
-      </c>
+      <c r="C2" s="92"/>
     </row>
     <row r="3">
       <c r="C3" s="92"/>
